--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0052.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0052.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Explosive Jar</t>
+          <t>Bình Nổ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Stadter</t>
+          <t>Người Stadter</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Boss Mao</t>
+          <t>Đầu Sỏ Mao</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Baby Roseshroom</t>
+          <t>Nấm Hồng Bé Nhỏ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Trunk</t>
+          <t>Thùng hàng</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Explorer Nathan</t>
+          <t>Nhà thám hiểm Nathan</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Advanced Supply Chest</t>
+          <t>Rương Vật Tư Cao Cấp</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Tung đồng xu</t>
+          <t>Ném đồng xu đi</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Optical Path Articulator</t>
+          <t>Bộ Điều Chỉnh Đường Truyền Ánh Sáng</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu trẻ</t>
+          <t>Nhà Nghiên Cứu Trẻ</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Concierge</t>
+          <t>Lễ Tân</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Strange White Cat</t>
+          <t>Con mèo trắng kỳ lạ</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Apprentice</t>
+          <t>Học Trò</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Flufftail Fox</t>
+          <t>Cáo đuôi bông</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Rời "Replica of Past Days"</t>
+          <t>Rời "Bản Sao Ngày Xưa"</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Angry Youth</t>
+          <t>Thanh niên nổi nóng</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hongjing</t>
+          <t>Hồng Kính</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Giáo viên giám sát</t>
+          <t>Giáo viên Giám sát</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>KU-Fight</t>
+          <t>KU-Chiến Đấu</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Exam Zone 3</t>
+          <t>Khu Vực Thi 3</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Flare Stone</t>
+          <t>Đá Lửa</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Wrong Data Wall</t>
+          <t>Bức Tường Dữ Liệu Lỗi</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>(Giữ) Bước vào màn tiếp theo</t>
+          <t>(Giữ) Bước vào chương tiếp theo</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Hologram Chiến Thuật</t>
+          <t>Bản Hologram Chiến Thuật</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Học sinh nhảy múa</t>
+          <t>Học Sinh Nhảy Múa</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Sea Apple</t>
+          <t>Táo Biển</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>KU-Roro the Firearm</t>
+          <t>Juebi Desert</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Aria Mummer</t>
+          <t>Diễn Viên Aria</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Thủ lĩnh lưu đày gian xảo</t>
+          <t>Thủ Lĩnh Kẻ Lưu Đày Xảo Quyệt</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Đứng dậy</t>
+          <t>Đứng dậy đi</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Anh ấy'mu</t>
+          <t>Hắn à, He'mu...</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Chạm vào giá sách</t>
+          <t>Chạm vào kệ sách</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Waxweaver Web</t>
+          <t>Mạng Dệt Sáp</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Nhân viên Kho C</t>
+          <t>Nhân viên Ngân hàng C</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Change Channel</t>
+          <t>Đổi Kênh</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Lucio</t>
+          <t>Lucio...</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Shadow Stepper</t>
+          <t>Bước Bóng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Dollmaker</t>
+          <t>Thợ làm búp bê</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đi qua cổng và đối mặt với Ebony Gatekeeper</t>
+          <t>Bước qua cánh cổng và đối mặt với Ebony Gatekeeper</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Tắt</t>
+          <t>Tắt đi</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Analyze Information</t>
+          <t>Phân Tích Thông Tin</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Fuqing</t>
+          <t>Phúc Khánh</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Small Golden Tree</t>
+          <t>Cây Vàng Nhỏ</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Cô gái Clang Bang</t>
+          <t>Cô Gái Ầm Dội</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Miss Clover</t>
+          <t>Chị Clover</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Inventor's Illusion</t>
+          <t>Ảo ảnh của Nhà phát minh</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Material-Rich Fishing Spot</t>
+          <t>Điểm Câu Cá Giàu Vật Liệu</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Guo</t>
+          <t>Quốc</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Jumpy Cushion</t>
+          <t>Đệm Nhún</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Tidal Heritage</t>
+          <t>Di sản Thủy Triều</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Bình tĩnh</t>
+          <t>Nhà nghiên cứu điềm đạm</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Exile Seeking Help</t>
+          <t>Lưu Đày Tìm Sự Giúp Đỡ</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nhân viên Ủ rũ</t>
+          <t>Gậy U Sầu</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>About Debiao</t>
+          <t>Về Debiao</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Sửa chữa</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Passing Acolyte</t>
+          <t>Tín Đồ Đi Qua</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Glowing Rocksteady Guardian</t>
+          <t>Người Bảo Hộ Đá Phát Quang</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Twin Lotus Seed</t>
+          <t>Hạt Sen Song Sinh</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Sương mù dày đặc chặn đường phía trước</t>
+          <t>Sương mù dày đặc chắn ngang phía trước.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Deliver Soliseed</t>
+          <t>Giao Hạt Soliseed</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Cautious Gladiator</t>
+          <t>Đấu Sĩ Thận Trọng</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Mysterious Sea Chest</t>
+          <t>Rương Biển Bí Ẩn</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Mời bạn đồng hành tham gia buổi lễ</t>
+          <t>Mời bạn bè cùng tham gia lễ hội</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Guowei</t>
+          <t>Quốc Vĩ</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Sea Apple</t>
+          <t>Táo Biển</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Fissured Ledge</t>
+          <t>Vách Đá Nứt</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Vào Mind Dive Arcade</t>
+          <t>Bước vào Khu Vực Tâm Trí Ảo</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Dấu vết Strange Dark Tide kỳ lạ</t>
+          <t>Dấu Vết Lạ Của Dark Tide</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Key Base</t>
+          <t>Căn Cứ Chính</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Fissured Ledge_Large</t>
+          <t>Vách Đá Nứt_Lớn</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Chiếc ghế mang hơi hướng đáng sợ</t>
+          <t>Một chiếc ghế toát ra khí thế uy nghiêm</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>: Phantasm Partita</t>
+          <t>: Partita Ảo Ảnh</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Golden Thiefbat</t>
+          <t>Dơi Trộm Vàng</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Sister Guang</t>
+          <t>Chị Quang</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Thành viên Đoàn kịch</t>
+          <t>Thành Viên Đoàn</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Kiểm tra bia đá</t>
+          <t>Kiểm tra tấm bia đá</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Mingyan</t>
+          <t>Minh Nghiêm</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Invade</t>
+          <t>Xâm nhập</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Deliverypon</t>
+          <t>Giao hàngpon</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Zhixing</t>
+          <t>Chí Hành</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>- Irideglow Contamination</t>
+          <t>Ô Nhiễm Irideglow</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Eager Commoner</t>
+          <t>Dân Thường Hăng Hái</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Midnight Ranger</t>
+          <t>Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tiếp tân Đấu giá</t>
+          <t>Nhân Viên Tiếp Nhận Đấu Giá</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Loong's Pearl</t>
+          <t>Ngọc Trai của Loong</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Vào Nhà máy Búp bê</t>
+          <t>Bước vào Nhà Máy Búp Bê</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>: The Forsworn</t>
+          <t>: Kẻ Phản Bội</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Về Tiến trình Khám phá của tôi</t>
+          <t>Về tiến độ thám hiểm của ta</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Chạm nhẹ</t>
+          <t>Chạm nhẹ nhàng</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Electro Predator</t>
+          <t>Thú Điện Khát Máu</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Đi lên lầu</t>
+          <t>Lên lầu</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Explorer Jones</t>
+          <t>Nhà thám hiểm Jones</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>"Undying Malice"</t>
+          <t>"Oán Hận Bất Diệt"</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Đến điểm thử thách</t>
+          <t>Tiến đến điểm thử thách</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Tiến đến trạm</t>
+          <t>Tiến đến trạm tiếp theo</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Vào Thế giới Than Thở</t>
+          <t>Bước vào Thế Giới Than Thở</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Bei Shi</t>
+          <t>Bắc Thi</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Bức tường vô hình bao phủ khu vực nhỏ</t>
+          <t>Tường vô hình bao quanh khu vực nhỏ</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Player Đội Entity</t>
+          <t>Đội Hình Thực Thể Người Chơi</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Lilan</t>
+          <t>Lý Lan</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Pastry Vendor</t>
+          <t>Người Bán Bánh</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Voidwing Moth</t>
+          <t>Bướm Voidwing</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Ancestor Tony</t>
+          <t>Tổ Tiên Tony</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Ordinary Bartender</t>
+          <t>Người Pha Chế Bình Thường</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Ski</t>
+          <t>Hologram Chiến Thuật: Ski</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Scarlet Velvet</t>
+          <t>Nhung Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Kronaclaw</t>
+          <t>Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Thiết bị cảnh báo tiến trình giải đố</t>
+          <t>Thiết bị cảnh báo tiến độ giải đố</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Test Floor 11</t>
+          <t>Tầng 11</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Lối chơi Center</t>
+          <t>Trung Tâm Chơi Game</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Portable Stove</t>
+          <t>Bếp Di Động</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Phagosite: Bipolarch</t>
+          <t>Phagosite: Song Cực Thạch</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Exile Cooking Utensils</t>
+          <t>Dụng Cụ Nấu Nướng Lưu Đày</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Vào Cục An ninh Công cộng</t>
+          <t>Bước vào Cục An Ninh Công Cộng</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Adventure Log Courier Truck</t>
+          <t>Xe tải chuyển phát Nhật ký phiêu lưu</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Enter Averardo Vault</t>
+          <t>Vào Kho Báu Averardo</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Bream</t>
+          <t>Cá Bream</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Kích hoạt Hub</t>
+          <t>Kích hoạt Trung Tâm Điều Khiển</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hua Lielang</t>
+          <t>Hoa Liệt Lang</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>- Nanh Độc Ác</t>
+          <t>- Nanh Vuốt Độc Ác</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Retriever</t>
+          <t>Người Thu Thập</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Ngồi xuống</t>
+          <t>Ngồi xuống đi</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Mingfang</t>
+          <t>Minh Phương</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Burrata Bakery</t>
+          <t>Tiệm Bánh Burrata</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Battle Stance</t>
+          <t>Tư Thế Chiến Đấu</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>"Ascend"</t>
+          <t>"Thăng Hoa"</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Bắt đầu quay phim</t>
+          <t>Bắt đầu bắn nào.</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Khám phá khu vực</t>
+          <t>Khám phá khu vực này</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Một bia mộ tỏa sáng rực rỡ như mặt trời</t>
+          <t>Ngôi mộ rực rỡ ánh dương chói lòa</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Thành viên đoàn nam</t>
+          <t>Thành viên Đoàn kịch</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Ngồi xuống để vào Vương quốc Wooly</t>
+          <t>Ngồi xuống để bước vào Vương Quốc Len</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Sigrika's Diary</t>
+          <t>Nhật ký của Sigrika</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Traveler Namipon</t>
+          <t>Lữ Khách Namipon</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Ký ức Nghỉ ngơi</t>
+          <t>Ký Ức Nghỉ Ngơi</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Bench Combination</t>
+          <t>Bộ Ghép Hình</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Qingxiang</t>
+          <t>Thanh Hương</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Vào Vòng lặp Thời gian</t>
+          <t>Bước vào Vòng Lặp Thời Gian</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Vitreum Dancer</t>
+          <t>Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Trang Trí Quán Cà Phê</t>
+          <t>Trang trí quán cà phê</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Nhân viên khách sạn lành nghề</t>
+          <t>Nhân viên khách sạn chuyên nghiệp</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Di chuyển sứa</t>
+          <t>Di chuyển con sứa</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Paradimensional Tacet Field Entrance</t>
+          <t>Lối Vào Tổ Tacet Siêu Không Gian</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Phantom: Cuddle Wuddle</t>
+          <t>Bóng Ma: Ôm Ấm</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Trò Chơi Thẻ</t>
+          <t>Trò chơi Thẻ</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Tiến vào Dimmr Plains</t>
+          <t>Đến Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Wooden Box</t>
+          <t>Hộp gỗ</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Gupan</t>
+          <t>Cổ Phan</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Rời Rabelle College</t>
+          <t>Rời khỏi Học viện Rabelle</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Lo Lắng</t>
+          <t>Nhà Nghiên Cứu Lo Lắng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Fanatic Shark Grunt</t>
+          <t>Lính Cá Mập Cuồng Tín</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Xiaoshu</t>
+          <t>Tiểu Thư</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Patch Bullet Launcher</t>
+          <t>Súng Phát Nổ Đạn Vá</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Theo sự hướng dẫn của Sumika đến khu vực tiếp theo</t>
+          <t>Đi theo sự hướng dẫn của Sumika đến khu vực tiếp theo</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Vào Hẻm Đen</t>
+          <t>Bước vào Ngõ Tối.</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Sales Champ</t>
+          <t>Quán Quân Bán Hàng</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Kiếm Pedestal</t>
+          <t>Bệ Kiếm</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Strange Box</t>
+          <t>Chiếc Hộp Bí Ẩn</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Người Dân Lo Lắng</t>
+          <t>Dân Thường Lo Âu</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Gladiator's Spear</t>
+          <t>Ngọn Giáo Đấu Sĩ</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Xem ghi chú do Ahab để lại</t>
+          <t>Xem lời nhắn Ahab để lại.</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Lời Thề Cindertide</t>
+          <t>Lời Thề Của Bão Lửa</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Diggy Duggy</t>
+          <t>Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Voidspawn: Twin Nova</t>
+          <t>Tacet Discord: Song Tử Kép</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Doubtful Audience</t>
+          <t>Khán Giả Nghi Ngờ</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Gourd</t>
+          <t>Bầu rượu</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Thử giao tiếp</t>
+          <t>Cố giao tiếp đi</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Giải thích lại cho tôi</t>
+          <t>Kể ta nghe thêm một lần nữa đi.</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Đi sạc</t>
+          <t>Tiến lên và sạc năng lượng đi</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Fusheng</t>
+          <t>Phục Sinh</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Tiến đến cấp độ tiếp theo</t>
+          <t>Tiến tới Cấp Độ Tiếp Theo</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Đứa Trẻ Tò Mò</t>
+          <t>Đứa trẻ tò mò</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Wreath</t>
+          <t>Vòng Hoa</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Qianxin</t>
+          <t>Kiền Tâm</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>: Mistfield Tunes</t>
+          <t>: Giai Điệu Sương Mù</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nồi hầm bị đổ</t>
+          <t>Canh bị đổ</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Aria Mummer</t>
+          <t>Diễn Viên Aria</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Stargazing</t>
+          <t>Ngắm sao</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Thiết bị laser</t>
+          <t>Thiết bị Laser</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Chơi Đàn Piano</t>
+          <t>Chơi đàn piano</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Composed Gladiator</t>
+          <t>Dũng Sĩ Điềm Tĩnh</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Kích hoạt Probe</t>
+          <t>Kích hoạt Máy Dò</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Frozen Soil Sample Vial</t>
+          <t>Lọ Mẫu Đất Đông Cứng</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Mời đấu</t>
+          <t>Mời thách đấu</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Serious Tuner</t>
+          <t>Điều Tần viên Nghiêm túc</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Gift Box</t>
+          <t>Hộp quà</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Dấu vết</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Lặn vào "Biển"</t>
+          <t>Lặn Xuống "Biển Cả"</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Erodorchid</t>
+          <t>Hoa Phong Lan Xói Mòn</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Grandpa Zou</t>
+          <t>Ông nội Zou</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Tương Tác</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Pressure Plate</t>
+          <t>Bản Áp Lực</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Action Planner</t>
+          <t>Bảng Kế Hoạch Hành Động</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Jingyue</t>
+          <t>Tinh Nguyệt</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Dấu vết khả nghi</t>
+          <t>Dấu Vết Đáng Ngờ</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Đến Tầng Trung</t>
+          <t>Tới Hạng Trung</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Cocky Pirate</t>
+          <t>Kẻ Cướp Biển Ngạo Mạn</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu hoảng loạn</t>
+          <t>Nhà nghiên cứu hoảng hốt</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Backwindow</t>
+          <t>Cửa sổ sau</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Thương nhân lo lắng</t>
+          <t>Thương Nhân Lo Âu</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Gravity Stream 50m</t>
+          <t>Dòng Trọng Lực 50m</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>The Chronicler</t>
+          <t>Biên Niên Sử Gia</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Zhiyuan</t>
+          <t>Chí Nguyên</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Nightmare: Mourning Aix</t>
+          <t>Ác Mộng: Mourning Aix</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Đến tầng giữa</t>
+          <t>Đến tầng trung</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Bảo cô gái đến thiết bị bên trái</t>
+          <t>Bảo cô bé đi đến thiết bị bên trái</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Wenshu</t>
+          <t>Văn Thư</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Ly Starfall cuối cùng</t>
+          <t>Ly rượu Ngôi Sao Rơi cuối cùng</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Lollo Logistics Courier</t>
+          <t>Nhân Viên Giao Hàng Lollo Hậu Cần</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Raw Meat</t>
+          <t>Thịt sống</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Care-Refusing Patient</t>
+          <t>Bệnh Nhân Từ Chối Điều Trị</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Preparations</t>
+          <t>Chuẩn bị</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>KU-Money Exchange</t>
+          <t>Sàn Giao Dịch KU-Money</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Pioneer Info</t>
+          <t>Thông Tin Tiên Phong</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Ivanck</t>
+          <t>Ivank</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Khách hàng nữ rụt rè</t>
+          <t>Khách Hàng Nữ E Ngại</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Lele</t>
+          <t>Lạc Lạc</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Pavo Plum</t>
+          <t>Mận Pavo</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Reasonable Fisherman</t>
+          <t>Ngư Phu Thấu Tình</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tough Exile</t>
+          <t>Lưu Đày Khắc Nghiệt</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Theo hướng dẫn của Sumika đến khu vực tiếp theo</t>
+          <t>Đi theo sự hướng dẫn của Sumika đến khu vực tiếp theo</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Phát</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Chainsaw</t>
+          <t>Cưa Xích</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Wind Circle</t>
+          <t>Vòng Gió</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Supply Chest</t>
+          <t>Rương cung cấp tiêu chuẩn</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Thực đơn cũ rách</t>
+          <t>Thực Đơn Rách Nát</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Hunter: Wind</t>
+          <t>Thợ Săn: Gió</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Giúp đỡ người hành hương</t>
+          <t>Giúp người hành hương.</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Sittable Stone</t>
+          <t>Đá Ngồi</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Thorns</t>
+          <t>Gai Nhọn</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Phantom Sovereign Mitosis</t>
+          <t>Sinh Vật Ảo Giác Tối Thượng</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Sabercat Prowler</t>
+          <t>Kẻ Rình Rập Mèo Đao</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Illusive Echo</t>
+          <t>Tiếng Vọng Ảo Ảnh</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Vào Command Rise</t>
+          <t>Bước vào Tháp Chỉ Huy</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Kích hoạt bảng điều khiển</t>
+          <t>Kích hoạt thiết bị đầu cuối.</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mảnh kính màu dính bẩn</t>
+          <t>Mảnh Kính Màu</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đóng cửa</t>
+          <t>Đóng cửa lại</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Bắt đầu thử thách Moon Shooter</t>
+          <t>Bắt Đầu Thử Thách Moon Shooter</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Colleen</t>
+          <t>Colleen.</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Nhân viên đoàn múa lân nghiêm túc</t>
+          <t>Thành Viên Đoàn Múa Lân Đứng Đắn</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Lấy nước ép</t>
+          <t>Lấy nước trái cây đi</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Vòng tính điểm</t>
+          <t>Vòng Điểm Số</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Vút Lên</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Havoc Drake</t>
+          <t>Drake Hỗn Loạn</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Academy Robot</t>
+          <t>Robot Học Viện</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nightmare: Roseshroom</t>
+          <t>Ác Mộng: Roseshroom</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Cold Acolyte</t>
+          <t>Tín Đồ Băng Giá</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Simulator Terminal</t>
+          <t>Thiết bị đầu cuối Mô phỏng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Gulpuff Relay Past Champions</t>
+          <t>Những Nhà Vô Địch Tiếp Sức Gulpuff Trước Đây</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Doumi</t>
+          <t>Đậu Mị</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>The Binder</t>
+          <t>Kẻ Ràng Buộc</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>: Yuanlong</t>
+          <t>: Viễn Long</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Black Shores Consultant</t>
+          <t>Cố Vấn Bờ Đen</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Xem xét những ghi chú ngâm nước</t>
+          <t>Xem xét những tờ ghi chép ngâm nước</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Survivor</t>
+          <t>Người sống sót</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Advanced Supply Pack</t>
+          <t>Gói Vật Tư Cao Cấp</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Điều tra thông điệp bên trong Terminal</t>
+          <t>Đọc thông điệp trong Thiết bị đầu cuối</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Rubbles</t>
+          <t>Mảnh vụn</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Young Dreadmane: Ice</t>
+          <t>Dreadmane Trẻ: Băng</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Tank Guardian: Dark</t>
+          <t>Hộ Vệ Thiết Giáp: Hắc Ám</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Qianyue</t>
+          <t>Kiền Nguyệt</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Hunter: Thunder</t>
+          <t>Thợ Săn: Sấm</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Terminal Technician</t>
+          <t>Kỹ Thuật Viên Thiết Bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>: "Uncle Henry"</t>
+          <t>: "Chú Henry"</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Steer</t>
+          <t>Điều khiển</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đứa trẻ nghịch ngợm</t>
+          <t>Đứa Trẻ Tinh Nghịch</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Fractsidus Cube</t>
+          <t>Khối Fractsidus</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Soliskin Sticker</t>
+          <t>Hình Dán Soliskin</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Cô gái đang đợi xe buýt</t>
+          <t>Cô gái đợi xe buýt</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
